--- a/examples/jpetstore-6/.understand-anything/doc-output/si-테이블정의서.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-테이블정의서.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="ACCOUNT 테이블" sheetId="1" r:id="rId1"/>
-    <sheet name="BANNERDATA 테이블" sheetId="2" r:id="rId2"/>
-    <sheet name="CATEGORY 테이블" sheetId="3" r:id="rId3"/>
-    <sheet name="INVENTORY 테이블" sheetId="4" r:id="rId4"/>
-    <sheet name="ITEM 테이블" sheetId="5" r:id="rId5"/>
-    <sheet name="LINEITEM 테이블" sheetId="6" r:id="rId6"/>
-    <sheet name="ORDERS 테이블" sheetId="7" r:id="rId7"/>
-    <sheet name="ORDERSTATUS 테이블" sheetId="8" r:id="rId8"/>
-    <sheet name="PRODUCT 테이블" sheetId="9" r:id="rId9"/>
-    <sheet name="PROFILE 테이블" sheetId="10" r:id="rId10"/>
-    <sheet name="SEQUENCE 테이블" sheetId="11" r:id="rId11"/>
-    <sheet name="SIGNON 테이블" sheetId="12" r:id="rId12"/>
-    <sheet name="SUPPLIER 테이블" sheetId="13" r:id="rId13"/>
+    <sheet name="문서정보" sheetId="1" r:id="rId1"/>
+    <sheet name="ACCOUNT 테이블" sheetId="2" r:id="rId2"/>
+    <sheet name="BANNERDATA 테이블" sheetId="3" r:id="rId3"/>
+    <sheet name="CATEGORY 테이블" sheetId="4" r:id="rId4"/>
+    <sheet name="INVENTORY 테이블" sheetId="5" r:id="rId5"/>
+    <sheet name="ITEM 테이블" sheetId="6" r:id="rId6"/>
+    <sheet name="LINEITEM 테이블" sheetId="7" r:id="rId7"/>
+    <sheet name="ORDERS 테이블" sheetId="8" r:id="rId8"/>
+    <sheet name="ORDERSTATUS 테이블" sheetId="9" r:id="rId9"/>
+    <sheet name="PRODUCT 테이블" sheetId="10" r:id="rId10"/>
+    <sheet name="PROFILE 테이블" sheetId="11" r:id="rId11"/>
+    <sheet name="SEQUENCE 테이블" sheetId="12" r:id="rId12"/>
+    <sheet name="SIGNON 테이블" sheetId="13" r:id="rId13"/>
+    <sheet name="SUPPLIER 테이블" sheetId="14" r:id="rId14"/>
   </sheets>
 </workbook>
 </file>
@@ -69,427 +70,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="58" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>컬럼</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>타입</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>신뢰도</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>근거</t>
+          <t>내용</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>userid</t>
+          <t>문서명</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="D2"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F2"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:37</t>
+          <t>SI 테이블정의서</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>방법론</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F3"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:38</t>
+          <t>si-standard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>firstname</t>
+          <t>소스 커밋</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F4"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:39</t>
+          <t>[미확인]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lastname</t>
+          <t>작성자 / 버전 / 작성일</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F5"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:40</t>
+          <t>[미확인] — 제출 전 사람이 채움</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>varchar(2)</t>
-        </is>
-      </c>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F6"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:41</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>본 파일의 지위</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>정적 스캔 스냅샷(원천 데이터) — 대시보드에서의 확정 편집은 반영되지 않음. 최신화는 /understand-docs 재실행.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>addr1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F7"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>addr2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>varchar(40)</t>
-        </is>
-      </c>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F8"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F9"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F10"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F11"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F12"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F13"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:48</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>신뢰도 표기</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>[확정]=정적 분석 근거(file:line) 보유, [추정]=추론, [미확인]=사람 채움 대상 — 사람 검수/사인오프 여부와 무관.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="59" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>컬럼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>신뢰도</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>productid</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D2"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F2"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:121</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="C3"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>→ CATEGORY(catid)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F3"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:122</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F4"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:123</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>descn</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>varchar(255)</t>
+        </is>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F5"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:124</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -699,10 +561,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H6"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -822,10 +685,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -945,10 +809,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1278,10 +1143,435 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H10"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="58" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>컬럼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>신뢰도</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>userid</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D2"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F2"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F3"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>firstname</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F4"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lastname</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F5"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>varchar(2)</t>
+        </is>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F6"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>addr1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F7"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>addr2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>varchar(40)</t>
+        </is>
+      </c>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F8"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F9"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F10"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F11"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F12"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>varchar(80)</t>
+        </is>
+      </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F13"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:48</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1401,10 +1691,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1554,10 +1845,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H4"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1677,10 +1969,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2078,10 +2371,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H12"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2295,10 +2589,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H6"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -3108,10 +3403,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H26"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -3295,192 +3591,6 @@
       </c>
     </row>
   </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="59" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>컬럼</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>타입</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>신뢰도</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>productid</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>varchar(10)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="D2"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F2"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:121</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>varchar(10)</t>
-        </is>
-      </c>
-      <c r="C3"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>→ CATEGORY(catid)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F3"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:122</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>varchar(80)</t>
-        </is>
-      </c>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F4"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:123</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>descn</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>varchar(255)</t>
-        </is>
-      </c>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F5"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>src/main/resources/database/jpetstore-hsqldb-data.sql:124</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:H5"/>
 </worksheet>
 </file>
--- a/examples/jpetstore-6/.understand-anything/doc-output/si-테이블정의서.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-테이블정의서.xlsx
@@ -118,7 +118,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>dfbb9822f7c17f41a39e96704f4ea4f455580278</t>
         </is>
       </c>
     </row>
